--- a/artfynd/A 38622-2026 artfynd.xlsx
+++ b/artfynd/A 38622-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,45 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69299233</v>
+        <v>137423891</v>
       </c>
       <c r="B2" t="n">
-        <v>92208</v>
+        <v>92442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>71</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Örnfloberget, Jmt</t>
+          <t>Örnfloberget, på höjden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515939</v>
+        <v>515900</v>
       </c>
       <c r="R2" t="n">
-        <v>6994960</v>
+        <v>6994884</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-05-18</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-05-18</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Observerad och artbestämd av Ulrika Westling. Inrapporterad av Johan Kjetselberg.</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,17 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>lövrik barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>170-årig tallskog i sydvänd brant</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -787,33 +772,33 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # granlåga # Picea abies</t>
+          <t>1 substratenheter # grov gammal tallåga med invallning av flera bränder, i spricka</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69299233</t>
+          <t>https://artportalen.se/Sighting/137423891</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69299232</v>
+        <v>69299233</v>
       </c>
       <c r="B3" t="n">
-        <v>91909</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -934,54 +919,54 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69299232</t>
+          <t>https://artportalen.se/Sighting/69299233</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69299231</v>
+        <v>137423905</v>
       </c>
       <c r="B4" t="n">
-        <v>99118</v>
+        <v>92452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Örnfloberget, Jmt</t>
+          <t>Örnflobergets sydsida, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515939</v>
+        <v>515805</v>
       </c>
       <c r="R4" t="n">
-        <v>6994960</v>
+        <v>6994968</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1005,17 +990,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-05-18</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-05-18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Observerad och artbestämd av Ulrika Westling. Inrapporterad av Johan Kjetselberg.</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +1009,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>lövrik barrnaturskog</t>
+          <t>olikåldrig tallnaturskog med lövinslag i blockig sydsluttning</t>
         </is>
       </c>
       <c r="AN4" t="n">
@@ -1037,22 +1017,272 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter</t>
+          <t>1 substratenheter # grov förrötad granlåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137423905</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>69299232</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Örnfloberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>515939</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6994960</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-05-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-05-18</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Observerad och artbestämd av Ulrika Westling. Inrapporterad av Johan Kjetselberg.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>lövrik barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>1 substratenheter # granlåga # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69299232</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>69299231</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Örnfloberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>515939</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6994960</v>
+      </c>
+      <c r="S6" t="n">
+        <v>30</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-05-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-05-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Observerad och artbestämd av Ulrika Westling. Inrapporterad av Johan Kjetselberg.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>lövrik barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>1 substratenheter</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/69299231</t>
         </is>
@@ -1063,6 +1293,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38622-2026 artfynd.xlsx
+++ b/artfynd/A 38622-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137423891</v>
       </c>
       <c r="B2" t="n">
-        <v>92442</v>
+        <v>92443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>137423905</v>
       </c>
       <c r="B4" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38622-2026 artfynd.xlsx
+++ b/artfynd/A 38622-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137423891</v>
       </c>
       <c r="B2" t="n">
-        <v>92443</v>
+        <v>92446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>137423905</v>
       </c>
       <c r="B4" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38622-2026 artfynd.xlsx
+++ b/artfynd/A 38622-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137423891</v>
       </c>
       <c r="B2" t="n">
-        <v>92446</v>
+        <v>92450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>137423905</v>
       </c>
       <c r="B4" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
